--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2020_atacama.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 02:06</t>
+    <t xml:space="preserve">2026-08-17 21:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2020_atacama.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:04</t>
+    <t xml:space="preserve">2026-09-06 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
